--- a/output/20261006_MK_2026_DACH_Clipping_Report___Analysis.xlsx
+++ b/output/20261006_MK_2026_DACH_Clipping_Report___Analysis.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46301.52022068301</v>
+        <v>46301.75791538948</v>
       </c>
     </row>
     <row r="8">

--- a/output/20261006_MK_2026_DACH_Clipping_Report___Analysis.xlsx
+++ b/output/20261006_MK_2026_DACH_Clipping_Report___Analysis.xlsx
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46301.75791538948</v>
+        <v>46301.94011925073</v>
       </c>
     </row>
     <row r="8">
@@ -1608,21 +1608,21 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46057</v>
+        <v>46067</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>geldmeisterin.com</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
+          <t>Mikrokredite als Anlagealternative</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1635,22 +1635,22 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
+          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
+          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1668,51 +1668,55 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Payoff</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1722,35 +1726,31 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46038</v>
+        <v>46044</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>E-fundresearch</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
+          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1759,31 +1759,31 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
+          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46035</v>
+        <v>46038</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>E-fundresearch</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
+          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -1792,31 +1792,31 @@
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
+          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46029</v>
+        <v>46035</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1825,26 +1825,26 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
+          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>portfolio institutionell</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Große Wirkung mit kleinen Krediten</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1858,31 +1858,31 @@
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
+          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46000</v>
+        <v>46028</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>portfolio institutionell</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Große Wirkung mit kleinen Krediten</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -1891,26 +1891,26 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
+          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1928,27 +1928,27 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
+          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>45997</v>
+        <v>45999</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -1961,27 +1961,27 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
+          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>45985</v>
+        <v>45997</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
+          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -1990,26 +1990,26 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
+          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>45973</v>
+        <v>45985</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
+          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2023,26 +2023,26 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
+          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>45848</v>
+        <v>45973</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Handelszeitung</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
+          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2056,42 +2056,75 @@
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
+          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
+        <v>45848</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Handelszeitung</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
         <v>45292</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>FONDS exklusiv Österreich</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Schwellenländer: Worauf es jetzt ankommt</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>https://www.fondsexklusiv.at/schwellenlaender-worauf-es-jetzt-ankommt/</t>
         </is>
@@ -2132,7 +2165,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Source: Sheet '2026 Clippings' (A9:G49)</t>
+          <t>Source: Sheet '2026 Clippings' (A9:G50)</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2183,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -2242,7 +2275,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
@@ -2260,10 +2293,10 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -2311,7 +2344,7 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -2398,7 +2431,7 @@
         <v>3</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>0.07317073170731707</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
@@ -2406,10 +2439,10 @@
         </is>
       </c>
       <c r="F27" s="8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.9512195121951219</v>
+        <v>0.9523809523809523</v>
       </c>
     </row>
     <row r="28">
@@ -2422,7 +2455,7 @@
         <v>12</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
@@ -2433,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="29">
@@ -2443,10 +2476,10 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
@@ -2457,7 +2490,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="30">
@@ -2470,7 +2503,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>0.04878048780487805</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
   </sheetData>
